--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.3.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.3.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.3.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0003.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0003.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,24 +609,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture restaur Ã© e et / ou pellicul Ã© e</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L'institut a microfilmÃ© le meilleur exemplaire</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -678,14 +682,10 @@
           <t>L157: suspicious token(s): 14X (letter/digit mix) :: 14X</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'il lui a ete possible de se procurer. Les d Ã© tails</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'il lui a Ã©tÃ© possible de se procurer. Les dÃ©tails</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: pas etÃ© filmÃ©es...</t>
+          <t>L96: punctuation artifact: repeated periods :: pas eté filmées...</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr"/>
@@ -749,14 +749,10 @@
           <t>L159: suspicious token(s): 18X (letter/digit mix) :: 18X</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaur Ã© es et / ou pellicul Ã© es</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: modification dans la mÃ©thode normale de filmage</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -790,12 +786,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -812,16 +808,8 @@
           <t>L161: suspicious token(s): 22X (letter/digit mix) :: 22X</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sont indiquÃ©s ci-dessous.</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -875,16 +863,8 @@
           <t>L163: suspicious token(s): 26X (letter/digit mix) :: 26X</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Reli Ã© avec d'autres documents</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture endommagÃ©e.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -938,16 +918,8 @@
           <t>L165: suspicious token(s): 30X (letter/digit mix) :: 30X</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: distorsion le long de la marge int Ã© rieure</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages endommagÃ©es</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1001,16 +973,8 @@
           <t>L171: suspicious token(s): 12X (letter/digit mix) :: 12X</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages color Ã© es. tachet ou piqu</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Couverture restaurÃ©e et/ou pelliculÃ©e</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1064,16 +1028,8 @@
           <t>L173: suspicious token(s): 16X (letter/digit mix) :: 16X</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages d Ã© tach Ã© es</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages restaurÃ©es et/ou pelliculÃ©es</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1083,7 +1039,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1105,12 +1061,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1127,16 +1083,8 @@
           <t>L175: suspicious token(s): 20X (letter/digit mix) :: 20X</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Qualit Ã© in Ã© gale de l'impression</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Cartes gÃ©ographiques en couleur</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
@@ -1169,7 +1117,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1178,7 +1126,7 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 20X (letter/digit mix) :: 20X ã€�</t>
+          <t>L112: suspicious token(s): 20X (letter/digit mix) :: 20X 、</t>
         </is>
       </c>
       <c r="I11" s="1" t="inlineStr">
@@ -1186,16 +1134,8 @@
           <t>L177: suspicious token(s): 24X (letter/digit mix) :: 24X</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Comprend du mar Ã© briel suppl Ã© mentaire</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages dÃ©colorÃ©es, tachetÃ©es ou piquÃ©es</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
@@ -1245,16 +1185,8 @@
           <t>L179: suspicious token(s): 28X (letter/digit mix) :: 28X</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Seule Ã© dition disponible</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pages dÃ©tachÃ©es</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr"/>
@@ -1304,16 +1236,8 @@
           <t>L181: suspicious token(s): 32X (letter/digit mix) :: 32X</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: etc. ont et Ã© film a nouveau de fa a</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: QualitÃ© inÃ©gale de l'impression</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr"/>
@@ -1359,22 +1283,14 @@
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il se peut que certaines pages blanches ajout Ã© es</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ReliÃ© avec d'autres documents</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr"/>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1410,16 +1326,8 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mais, lorsque cela Ã© tait possible. ces pages n'ont</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Comprend du matÃ©riel supplÃ©mentaire</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr"/>
@@ -1461,16 +1369,8 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: pas etÃ© filmÃ©es...</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La reliure serrÃ©e peut causer de l'ombre ou de la</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr"/>
@@ -1512,16 +1412,8 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce document est filmÃ© au taux de rÃ©duction indiquÃ© ci-ci-dessous.</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: distorsion le long de la marge intÃ©rieure</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr"/>
@@ -1537,289 +1429,6 @@
       <c r="X17" s="1" t="inlineStr"/>
       <c r="Y17" s="1" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr"/>
-      <c r="D18" s="1" t="inlineStr"/>
-      <c r="E18" s="1" t="inlineStr"/>
-      <c r="F18" s="1" t="inlineStr"/>
-      <c r="G18" s="1" t="inlineStr"/>
-      <c r="H18" s="1" t="inlineStr"/>
-      <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 20X (letter/digit mix) :: 20X ã€�</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Seule Ã©dition disponible</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr"/>
-      <c r="M18" s="1" t="inlineStr"/>
-      <c r="N18" s="1" t="inlineStr"/>
-      <c r="O18" s="1" t="inlineStr"/>
-      <c r="P18" s="1" t="inlineStr"/>
-      <c r="Q18" s="1" t="inlineStr"/>
-      <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
-      <c r="T18" s="1" t="inlineStr"/>
-      <c r="U18" s="1" t="inlineStr"/>
-      <c r="V18" s="1" t="inlineStr"/>
-      <c r="W18" s="1" t="inlineStr"/>
-      <c r="X18" s="1" t="inlineStr"/>
-      <c r="Y18" s="1" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr"/>
-      <c r="D19" s="1" t="inlineStr"/>
-      <c r="E19" s="1" t="inlineStr"/>
-      <c r="F19" s="1" t="inlineStr"/>
-      <c r="G19" s="1" t="inlineStr"/>
-      <c r="H19" s="1" t="inlineStr"/>
-      <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr"/>
-      <c r="O19" s="1" t="inlineStr"/>
-      <c r="P19" s="1" t="inlineStr"/>
-      <c r="Q19" s="1" t="inlineStr"/>
-      <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="1" t="inlineStr"/>
-      <c r="T19" s="1" t="inlineStr"/>
-      <c r="U19" s="1" t="inlineStr"/>
-      <c r="V19" s="1" t="inlineStr"/>
-      <c r="W19" s="1" t="inlineStr"/>
-      <c r="X19" s="1" t="inlineStr"/>
-      <c r="Y19" s="1" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L131: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: etc., ont Ã©tÃ© filmÃ©es Ã nouveau de faÃ§on Ã</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr"/>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr"/>
-      <c r="Y20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: II se peut que certaines pages blanches ajoutÃ©es</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr"/>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr"/>
-      <c r="Y21" s="1" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: mais, lorsque cela Ã©tait possible, cas pages nâ€™ont</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
-      <c r="U22" s="1" t="inlineStr"/>
-      <c r="V22" s="1" t="inlineStr"/>
-      <c r="W22" s="1" t="inlineStr"/>
-      <c r="X22" s="1" t="inlineStr"/>
-      <c r="Y22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pas Ã©tÃ© filmÃ©es.</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
-      <c r="U23" s="1" t="inlineStr"/>
-      <c r="V23" s="1" t="inlineStr"/>
-      <c r="W23" s="1" t="inlineStr"/>
-      <c r="X23" s="1" t="inlineStr"/>
-      <c r="Y23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr"/>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Commentaires supplÃ©mentaires;</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr"/>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr"/>
-      <c r="U24" s="1" t="inlineStr"/>
-      <c r="V24" s="1" t="inlineStr"/>
-      <c r="W24" s="1" t="inlineStr"/>
-      <c r="X24" s="1" t="inlineStr"/>
-      <c r="Y24" s="1" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce document est filmÃ© au taux de rÃ©duction indiquÃ© ci-dessous.</t>
-        </is>
-      </c>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr"/>
-      <c r="R25" s="1" t="inlineStr"/>
-      <c r="S25" s="1" t="inlineStr"/>
-      <c r="T25" s="1" t="inlineStr"/>
-      <c r="U25" s="1" t="inlineStr"/>
-      <c r="V25" s="1" t="inlineStr"/>
-      <c r="W25" s="1" t="inlineStr"/>
-      <c r="X25" s="1" t="inlineStr"/>
-      <c r="Y25" s="1" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr"/>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr"/>
-      <c r="U26" s="1" t="inlineStr"/>
-      <c r="V26" s="1" t="inlineStr"/>
-      <c r="W26" s="1" t="inlineStr"/>
-      <c r="X26" s="1" t="inlineStr"/>
-      <c r="Y26" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
